--- a/docs/03-BOM/BOM_edit.xlsx
+++ b/docs/03-BOM/BOM_edit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arizonastateu-my.sharepoint.com/personal/nsgarde_sundevils_asu_edu/Documents/EGR304/Individual Subsystem/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="247" documentId="8_{E0E6FDB3-805D-43F3-893B-A328E29ED786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{123D3182-E5F9-4501-BD4B-D23FE7AD8499}"/>
+  <xr:revisionPtr revIDLastSave="355" documentId="8_{E0E6FDB3-805D-43F3-893B-A328E29ED786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5001A3CF-64C8-4212-A661-E46F75F23ABC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="95">
   <si>
     <t>Bill of Materials Example</t>
   </si>
@@ -146,9 +146,6 @@
     <t>D1,D2,D3,D4,D5,D6,D7,D8,D9,10,D11</t>
   </si>
   <si>
-    <t>1.2A fuse</t>
-  </si>
-  <si>
     <t>datasheet</t>
   </si>
   <si>
@@ -164,30 +161,6 @@
     <t>Fuse holder</t>
   </si>
   <si>
-    <t>031301.2MXP</t>
-  </si>
-  <si>
-    <t>Littelfuse Inc.</t>
-  </si>
-  <si>
-    <t>031301.2MXP-ND</t>
-  </si>
-  <si>
-    <t>F2,F2,F5,F7,F8</t>
-  </si>
-  <si>
-    <t>700mA fuse</t>
-  </si>
-  <si>
-    <t>0235.700MXP</t>
-  </si>
-  <si>
-    <t>F4719-ND</t>
-  </si>
-  <si>
-    <t>F3,F4,F6</t>
-  </si>
-  <si>
     <t>12 pin terminal block</t>
   </si>
   <si>
@@ -197,9 +170,6 @@
     <t>0397730012-ND</t>
   </si>
   <si>
-    <t>J1</t>
-  </si>
-  <si>
     <t>BJT transistor</t>
   </si>
   <si>
@@ -285,6 +255,69 @@
   </si>
   <si>
     <t>36-4952-ND</t>
+  </si>
+  <si>
+    <t>CNC tech</t>
+  </si>
+  <si>
+    <t>243-16-1-03</t>
+  </si>
+  <si>
+    <t>1175-1477-ND</t>
+  </si>
+  <si>
+    <t>16-pin DIP socket</t>
+  </si>
+  <si>
+    <t>SPST Switch</t>
+  </si>
+  <si>
+    <t>C&amp;K</t>
+  </si>
+  <si>
+    <t>S101031MS02Q</t>
+  </si>
+  <si>
+    <t>CKN10658-ND</t>
+  </si>
+  <si>
+    <t>10-pin header</t>
+  </si>
+  <si>
+    <t>SparkFun Electronics</t>
+  </si>
+  <si>
+    <t>no datasheet</t>
+  </si>
+  <si>
+    <t>1568-11896-ND</t>
+  </si>
+  <si>
+    <t>F1, F2, F3</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>SPKM.10.8.A1</t>
+  </si>
+  <si>
+    <t>CR1</t>
+  </si>
+  <si>
+    <t>U4,U5</t>
+  </si>
+  <si>
+    <t>SW1</t>
+  </si>
+  <si>
+    <t>TP1,TP2,TP3,TP4,TP5,TP6,TP7,TP8,TP9,TP10,TP11,TP12,TP13,TP14,TP15,TP16,TP17,TP18,TP19</t>
   </si>
 </sst>
 </file>
@@ -365,13 +398,15 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -709,11 +744,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q102"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -733,25 +769,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -817,26 +853,26 @@
         <v>0.26</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" ref="D3:D101" si="0">B3*C3</f>
+        <f t="shared" ref="D3:D27" si="0">B3*C3</f>
         <v>1.82</v>
       </c>
       <c r="E3" s="4">
         <v>0</v>
       </c>
       <c r="F3" s="4">
-        <f t="shared" ref="F3:F101" si="1">B3*E3</f>
+        <f t="shared" ref="F3:F27" si="1">B3*E3</f>
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="6" t="s">
         <v>21</v>
       </c>
       <c r="K3" s="2" t="s">
@@ -855,17 +891,17 @@
     </row>
     <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="E4" s="4">
         <v>0</v>
@@ -875,44 +911,44 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>27</v>
+        <v>39</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="2"/>
+        <v>40</v>
+      </c>
       <c r="N4" s="5"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="3"/>
+      <c r="P4" s="3">
+        <v>0</v>
+      </c>
       <c r="Q4" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>12.69</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12.69</v>
       </c>
       <c r="E5" s="4">
         <v>0</v>
@@ -922,44 +958,45 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="H5">
+        <v>397730012</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>44</v>
+      </c>
       <c r="N5" s="5"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="3"/>
+      <c r="P5" s="3">
+        <f t="shared" ref="P5:P13" si="2">O5-B5</f>
+        <v>-1</v>
+      </c>
       <c r="Q5" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="B6" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6" s="4">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
@@ -969,43 +1006,45 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>27</v>
+        <v>55</v>
+      </c>
+      <c r="H6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>57</v>
+      </c>
       <c r="N6" s="5"/>
-      <c r="P6" s="3"/>
+      <c r="P6" s="3">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
       <c r="Q6" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" s="4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="E7" s="4">
         <v>0</v>
@@ -1014,44 +1053,46 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>27</v>
+      <c r="G7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="L7" t="s">
+        <v>62</v>
+      </c>
       <c r="N7" s="5"/>
-      <c r="P7" s="3"/>
+      <c r="P7" s="3">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
       <c r="Q7" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C8" s="4">
-        <v>0</v>
+        <v>13.56</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13.56</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
@@ -1060,45 +1101,46 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>27</v>
+      <c r="G8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="L8" t="s">
+        <v>66</v>
+      </c>
       <c r="N8" s="5"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="2" t="s">
-        <v>36</v>
+      <c r="P8" s="3">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B9" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4">
-        <v>0.99</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>19.8</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
@@ -1107,45 +1149,46 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" t="s">
-        <v>44</v>
+      <c r="G9" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="8" t="s">
-        <v>38</v>
+      <c r="J9" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L9" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" s="2"/>
+        <v>67</v>
+      </c>
       <c r="N9" s="5"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="2" t="s">
-        <v>46</v>
+      <c r="P9" s="3">
+        <f t="shared" si="2"/>
+        <v>-4</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C10" s="4">
-        <v>0.61</v>
+        <v>0.38</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>6.1</v>
+        <v>0.76</v>
       </c>
       <c r="E10" s="4">
         <v>0</v>
@@ -1155,41 +1198,45 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>38</v>
+      <c r="J10" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>41</v>
+      <c r="L10" t="s">
+        <v>76</v>
       </c>
       <c r="N10" s="5"/>
       <c r="P10" s="3">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C11" s="4">
-        <v>0.52</v>
+        <v>4.3</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="E11" s="4">
         <v>0</v>
@@ -1198,46 +1245,46 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G11" t="s">
-        <v>44</v>
+      <c r="G11" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>38</v>
+      <c r="J11" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L11" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="N11" s="5"/>
       <c r="P11" s="3">
-        <f t="shared" ref="P10:P101" si="2">O11-B11</f>
-        <v>-10</v>
+        <f t="shared" si="2"/>
+        <v>-1</v>
       </c>
       <c r="Q11" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B12" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C12" s="4">
-        <v>12.69</v>
+        <v>0.8</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>12.69</v>
+        <v>8</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -1247,45 +1294,45 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="H12">
-        <v>397730012</v>
-      </c>
-      <c r="I12" s="8" t="s">
+        <v>11896</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>38</v>
+      <c r="J12" t="s">
+        <v>84</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="N12" s="5"/>
       <c r="P12" s="3">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="Q12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C13" s="4">
-        <v>0</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.3999999999999995</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
@@ -1295,55 +1342,58 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>27</v>
+        <v>72</v>
+      </c>
+      <c r="H13">
+        <v>4952</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="L13" t="s">
+        <v>73</v>
       </c>
       <c r="N13" s="5"/>
       <c r="P13" s="3">
         <f t="shared" si="2"/>
-        <v>-1</v>
+        <v>-25</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C14" s="4">
         <v>0</v>
       </c>
       <c r="D14" s="4">
-        <f t="shared" ref="D14" si="3">B14*C14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
       </c>
       <c r="F14" s="4">
-        <f t="shared" ref="F14" si="4">B14*E14</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H14" t="s">
-        <v>57</v>
+      <c r="H14" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>27</v>
@@ -1357,18 +1407,20 @@
       <c r="L14" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="M14" s="2"/>
       <c r="N14" s="5"/>
-      <c r="P14" s="3">
-        <f t="shared" si="2"/>
-        <v>-1</v>
+      <c r="O14" s="2"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="B15" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C15" s="4">
         <v>0</v>
@@ -1402,18 +1454,20 @@
       <c r="L15" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="M15" s="2"/>
       <c r="N15" s="5"/>
-      <c r="P15" s="3">
-        <f t="shared" si="2"/>
-        <v>-10</v>
+      <c r="O15" s="2"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="B16" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C16" s="4">
         <v>0</v>
@@ -1447,15 +1501,16 @@
       <c r="L16" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="M16" s="2"/>
       <c r="N16" s="5"/>
-      <c r="P16" s="3">
-        <f t="shared" si="2"/>
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="B17" s="3">
         <v>5</v>
@@ -1492,18 +1547,19 @@
       <c r="L17" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="M17" s="2"/>
       <c r="N17" s="5"/>
-      <c r="P17" s="3">
-        <f t="shared" si="2"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+      <c r="Q17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="B18" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C18" s="4">
         <v>0</v>
@@ -1537,18 +1593,20 @@
       <c r="L18" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="M18" s="2"/>
       <c r="N18" s="5"/>
-      <c r="P18" s="3">
-        <f t="shared" si="2"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O18" s="2"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B19" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C19" s="4">
         <v>0</v>
@@ -1567,8 +1625,8 @@
       <c r="G19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>27</v>
+      <c r="H19" t="s">
+        <v>46</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>27</v>
@@ -1584,16 +1642,19 @@
       </c>
       <c r="N19" s="5"/>
       <c r="P19" s="3">
-        <f t="shared" si="2"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f t="shared" ref="P19:P50" si="3">O19-B19</f>
+        <v>-1</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B20" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C20" s="4">
         <v>0</v>
@@ -1612,8 +1673,8 @@
       <c r="G20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>27</v>
+      <c r="H20" t="s">
+        <v>47</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>27</v>
@@ -1629,23 +1690,26 @@
       </c>
       <c r="N20" s="5"/>
       <c r="P20" s="3">
-        <f t="shared" si="2"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>-1</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B21" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C21" s="4">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="E21" s="4">
         <v>0</v>
@@ -1655,35 +1719,35 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21" t="s">
-        <v>66</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>38</v>
+        <v>27</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" t="s">
-        <v>67</v>
+        <v>27</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="N21" s="5"/>
       <c r="P21" s="3">
-        <f t="shared" si="2"/>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="B22" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C22" s="4">
         <v>0</v>
@@ -1719,23 +1783,23 @@
       </c>
       <c r="N22" s="5"/>
       <c r="P22" s="3">
-        <f t="shared" si="2"/>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B23" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C23" s="4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -1744,43 +1808,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G23" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" t="s">
-        <v>69</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>38</v>
+      <c r="G23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L23" t="s">
-        <v>72</v>
+        <v>27</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="N23" s="5"/>
       <c r="P23" s="3">
-        <f t="shared" si="2"/>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C24" s="4">
-        <v>13.56</v>
+        <v>0</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>13.56</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -1789,43 +1853,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G24" t="s">
-        <v>74</v>
-      </c>
-      <c r="H24" t="s">
-        <v>75</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>38</v>
+      <c r="G24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L24" t="s">
-        <v>76</v>
+        <v>27</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="N24" s="5"/>
       <c r="P24" s="3">
-        <f t="shared" si="2"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="B25" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="4">
-        <v>0.57999999999999996</v>
+        <v>0</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>2.3199999999999998</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -1835,42 +1899,42 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H25" t="s">
-        <v>78</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>38</v>
+        <v>27</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L25" t="s">
-        <v>77</v>
+        <v>27</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="N25" s="5"/>
       <c r="P25" s="3">
-        <f t="shared" si="2"/>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="B26" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C26" s="4">
-        <v>0.17599999999999999</v>
+        <v>0</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>4.3999999999999995</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -1880,1405 +1944,1008 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H26">
-        <v>4952</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>38</v>
+        <v>27</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L26" t="s">
-        <v>83</v>
+        <v>27</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="N26" s="5"/>
       <c r="P26" s="3">
-        <f t="shared" si="2"/>
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
+        <f t="shared" si="3"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="3">
+        <v>4</v>
+      </c>
+      <c r="C27" s="4">
+        <v>0</v>
+      </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E27" s="4"/>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
       <c r="F27" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="G27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="N27" s="5"/>
       <c r="P27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F28" s="4"/>
       <c r="N28" s="5"/>
       <c r="P28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B29" s="3"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F29" s="4"/>
       <c r="N29" s="5"/>
       <c r="P29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B30" s="3"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F30" s="4"/>
+      <c r="H30" s="6"/>
       <c r="N30" s="5"/>
       <c r="P30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B31" s="3"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F31" s="4"/>
+      <c r="H31" s="6"/>
       <c r="N31" s="5"/>
       <c r="P31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B32" s="3"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F32" s="4"/>
+      <c r="H32" s="6"/>
       <c r="N32" s="5"/>
       <c r="P32" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B33" s="3"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F33" s="4"/>
       <c r="N33" s="5"/>
       <c r="P33" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B34" s="3"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F34" s="4"/>
       <c r="N34" s="5"/>
       <c r="P34" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F35" s="4"/>
       <c r="N35" s="5"/>
       <c r="P35" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B36" s="3"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F36" s="4"/>
       <c r="N36" s="5"/>
       <c r="P36" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B37" s="3"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F37" s="4"/>
       <c r="N37" s="5"/>
       <c r="P37" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B38" s="3"/>
       <c r="C38" s="4"/>
-      <c r="D38" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D38" s="4"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F38" s="4"/>
       <c r="N38" s="5"/>
       <c r="P38" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B39" s="3"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D39" s="4"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F39" s="4"/>
       <c r="N39" s="5"/>
       <c r="P39" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B40" s="3"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D40" s="4"/>
       <c r="E40" s="4"/>
-      <c r="F40" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F40" s="4"/>
       <c r="N40" s="5"/>
       <c r="P40" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B41" s="3"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D41" s="4"/>
       <c r="E41" s="4"/>
-      <c r="F41" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F41" s="4"/>
       <c r="N41" s="5"/>
       <c r="P41" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B42" s="3"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D42" s="4"/>
       <c r="E42" s="4"/>
-      <c r="F42" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F42" s="4"/>
       <c r="N42" s="5"/>
       <c r="P42" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B43" s="3"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D43" s="4"/>
       <c r="E43" s="4"/>
-      <c r="F43" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F43" s="4"/>
       <c r="N43" s="5"/>
       <c r="P43" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B44" s="3"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D44" s="4"/>
       <c r="E44" s="4"/>
-      <c r="F44" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F44" s="4"/>
       <c r="N44" s="5"/>
       <c r="P44" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B45" s="3"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="F45" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F45" s="4"/>
       <c r="N45" s="5"/>
       <c r="P45" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B46" s="3"/>
       <c r="C46" s="4"/>
-      <c r="D46" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D46" s="4"/>
       <c r="E46" s="4"/>
-      <c r="F46" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F46" s="4"/>
       <c r="N46" s="5"/>
       <c r="P46" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B47" s="3"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D47" s="4"/>
       <c r="E47" s="4"/>
-      <c r="F47" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F47" s="4"/>
       <c r="N47" s="5"/>
       <c r="P47" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B48" s="3"/>
       <c r="C48" s="4"/>
-      <c r="D48" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D48" s="4"/>
       <c r="E48" s="4"/>
-      <c r="F48" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F48" s="4"/>
       <c r="N48" s="5"/>
       <c r="P48" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B49" s="3"/>
       <c r="C49" s="4"/>
-      <c r="D49" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F49" s="4"/>
       <c r="N49" s="5"/>
       <c r="P49" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B50" s="3"/>
       <c r="C50" s="4"/>
-      <c r="D50" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D50" s="4"/>
       <c r="E50" s="4"/>
-      <c r="F50" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F50" s="4"/>
       <c r="N50" s="5"/>
       <c r="P50" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B51" s="3"/>
       <c r="C51" s="4"/>
-      <c r="D51" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D51" s="4"/>
       <c r="E51" s="4"/>
-      <c r="F51" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F51" s="4"/>
       <c r="N51" s="5"/>
       <c r="P51" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="P51:P82" si="4">O51-B51</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B52" s="3"/>
       <c r="C52" s="4"/>
-      <c r="D52" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D52" s="4"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F52" s="4"/>
       <c r="N52" s="5"/>
       <c r="P52" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B53" s="3"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F53" s="4"/>
       <c r="N53" s="5"/>
       <c r="P53" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B54" s="3"/>
       <c r="C54" s="4"/>
-      <c r="D54" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D54" s="4"/>
       <c r="E54" s="4"/>
-      <c r="F54" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F54" s="4"/>
       <c r="N54" s="5"/>
       <c r="P54" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B55" s="3"/>
       <c r="C55" s="4"/>
-      <c r="D55" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D55" s="4"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F55" s="4"/>
       <c r="N55" s="5"/>
       <c r="P55" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B56" s="3"/>
       <c r="C56" s="4"/>
-      <c r="D56" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D56" s="4"/>
       <c r="E56" s="4"/>
-      <c r="F56" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F56" s="4"/>
       <c r="N56" s="5"/>
       <c r="P56" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B57" s="3"/>
       <c r="C57" s="4"/>
-      <c r="D57" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D57" s="4"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F57" s="4"/>
       <c r="N57" s="5"/>
       <c r="P57" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B58" s="3"/>
       <c r="C58" s="4"/>
-      <c r="D58" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D58" s="4"/>
       <c r="E58" s="4"/>
-      <c r="F58" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F58" s="4"/>
       <c r="N58" s="5"/>
       <c r="P58" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B59" s="3"/>
       <c r="C59" s="4"/>
-      <c r="D59" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D59" s="4"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F59" s="4"/>
       <c r="N59" s="5"/>
       <c r="P59" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B60" s="3"/>
       <c r="C60" s="4"/>
-      <c r="D60" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D60" s="4"/>
       <c r="E60" s="4"/>
-      <c r="F60" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F60" s="4"/>
       <c r="N60" s="5"/>
       <c r="P60" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B61" s="3"/>
       <c r="C61" s="4"/>
-      <c r="D61" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D61" s="4"/>
       <c r="E61" s="4"/>
-      <c r="F61" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F61" s="4"/>
       <c r="N61" s="5"/>
       <c r="P61" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B62" s="3"/>
       <c r="C62" s="4"/>
-      <c r="D62" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D62" s="4"/>
       <c r="E62" s="4"/>
-      <c r="F62" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F62" s="4"/>
       <c r="N62" s="5"/>
       <c r="P62" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B63" s="3"/>
       <c r="C63" s="4"/>
-      <c r="D63" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D63" s="4"/>
       <c r="E63" s="4"/>
-      <c r="F63" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F63" s="4"/>
       <c r="N63" s="5"/>
       <c r="P63" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B64" s="3"/>
       <c r="C64" s="4"/>
-      <c r="D64" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D64" s="4"/>
       <c r="E64" s="4"/>
-      <c r="F64" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F64" s="4"/>
       <c r="N64" s="5"/>
       <c r="P64" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B65" s="3"/>
       <c r="C65" s="4"/>
-      <c r="D65" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D65" s="4"/>
       <c r="E65" s="4"/>
-      <c r="F65" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F65" s="4"/>
       <c r="N65" s="5"/>
       <c r="P65" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B66" s="3"/>
       <c r="C66" s="4"/>
-      <c r="D66" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D66" s="4"/>
       <c r="E66" s="4"/>
-      <c r="F66" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F66" s="4"/>
       <c r="N66" s="5"/>
       <c r="P66" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B67" s="3"/>
       <c r="C67" s="4"/>
-      <c r="D67" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D67" s="4"/>
       <c r="E67" s="4"/>
-      <c r="F67" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F67" s="4"/>
       <c r="N67" s="5"/>
       <c r="P67" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B68" s="3"/>
       <c r="C68" s="4"/>
-      <c r="D68" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D68" s="4"/>
       <c r="E68" s="4"/>
-      <c r="F68" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F68" s="4"/>
       <c r="N68" s="5"/>
       <c r="P68" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B69" s="3"/>
       <c r="C69" s="4"/>
-      <c r="D69" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D69" s="4"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F69" s="4"/>
       <c r="N69" s="5"/>
       <c r="P69" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B70" s="3"/>
       <c r="C70" s="4"/>
-      <c r="D70" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F70" s="4"/>
       <c r="N70" s="5"/>
       <c r="P70" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B71" s="3"/>
       <c r="C71" s="4"/>
-      <c r="D71" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D71" s="4"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F71" s="4"/>
       <c r="N71" s="5"/>
       <c r="P71" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B72" s="3"/>
       <c r="C72" s="4"/>
-      <c r="D72" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D72" s="4"/>
       <c r="E72" s="4"/>
-      <c r="F72" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F72" s="4"/>
       <c r="N72" s="5"/>
       <c r="P72" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B73" s="3"/>
       <c r="C73" s="4"/>
-      <c r="D73" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F73" s="4"/>
       <c r="N73" s="5"/>
       <c r="P73" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B74" s="3"/>
       <c r="C74" s="4"/>
-      <c r="D74" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D74" s="4"/>
       <c r="E74" s="4"/>
-      <c r="F74" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F74" s="4"/>
       <c r="N74" s="5"/>
       <c r="P74" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B75" s="3"/>
       <c r="C75" s="4"/>
-      <c r="D75" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D75" s="4"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F75" s="4"/>
       <c r="N75" s="5"/>
       <c r="P75" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B76" s="3"/>
       <c r="C76" s="4"/>
-      <c r="D76" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D76" s="4"/>
       <c r="E76" s="4"/>
-      <c r="F76" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F76" s="4"/>
       <c r="N76" s="5"/>
       <c r="P76" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B77" s="3"/>
       <c r="C77" s="4"/>
-      <c r="D77" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D77" s="4"/>
       <c r="E77" s="4"/>
-      <c r="F77" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F77" s="4"/>
       <c r="N77" s="5"/>
       <c r="P77" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B78" s="3"/>
       <c r="C78" s="4"/>
-      <c r="D78" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D78" s="4"/>
       <c r="E78" s="4"/>
-      <c r="F78" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F78" s="4"/>
       <c r="N78" s="5"/>
       <c r="P78" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B79" s="3"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D79" s="4"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F79" s="4"/>
       <c r="N79" s="5"/>
       <c r="P79" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B80" s="3"/>
       <c r="C80" s="4"/>
-      <c r="D80" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D80" s="4"/>
       <c r="E80" s="4"/>
-      <c r="F80" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F80" s="4"/>
       <c r="N80" s="5"/>
       <c r="P80" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B81" s="3"/>
       <c r="C81" s="4"/>
-      <c r="D81" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D81" s="4"/>
       <c r="E81" s="4"/>
-      <c r="F81" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F81" s="4"/>
       <c r="N81" s="5"/>
       <c r="P81" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B82" s="3"/>
       <c r="C82" s="4"/>
-      <c r="D82" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D82" s="4"/>
       <c r="E82" s="4"/>
-      <c r="F82" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F82" s="4"/>
       <c r="N82" s="5"/>
       <c r="P82" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B83" s="3"/>
       <c r="C83" s="4"/>
-      <c r="D83" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D83" s="4"/>
       <c r="E83" s="4"/>
-      <c r="F83" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F83" s="4"/>
       <c r="N83" s="5"/>
       <c r="P83" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="P83:P102" si="5">O83-B83</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B84" s="3"/>
       <c r="C84" s="4"/>
-      <c r="D84" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D84" s="4"/>
       <c r="E84" s="4"/>
-      <c r="F84" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F84" s="4"/>
       <c r="N84" s="5"/>
       <c r="P84" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B85" s="3"/>
       <c r="C85" s="4"/>
-      <c r="D85" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D85" s="4"/>
       <c r="E85" s="4"/>
-      <c r="F85" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F85" s="4"/>
       <c r="N85" s="5"/>
       <c r="P85" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B86" s="3"/>
       <c r="C86" s="4"/>
-      <c r="D86" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D86" s="4"/>
       <c r="E86" s="4"/>
-      <c r="F86" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F86" s="4"/>
       <c r="N86" s="5"/>
       <c r="P86" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B87" s="3"/>
       <c r="C87" s="4"/>
-      <c r="D87" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D87" s="4"/>
       <c r="E87" s="4"/>
-      <c r="F87" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F87" s="4"/>
       <c r="N87" s="5"/>
       <c r="P87" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B88" s="3"/>
       <c r="C88" s="4"/>
-      <c r="D88" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D88" s="4"/>
       <c r="E88" s="4"/>
-      <c r="F88" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F88" s="4"/>
       <c r="N88" s="5"/>
       <c r="P88" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B89" s="3"/>
       <c r="C89" s="4"/>
-      <c r="D89" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D89" s="4"/>
       <c r="E89" s="4"/>
-      <c r="F89" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F89" s="4"/>
       <c r="N89" s="5"/>
       <c r="P89" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B90" s="3"/>
       <c r="C90" s="4"/>
-      <c r="D90" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D90" s="4"/>
       <c r="E90" s="4"/>
-      <c r="F90" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F90" s="4"/>
       <c r="N90" s="5"/>
       <c r="P90" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B91" s="3"/>
       <c r="C91" s="4"/>
-      <c r="D91" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D91" s="4"/>
       <c r="E91" s="4"/>
-      <c r="F91" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F91" s="4"/>
       <c r="N91" s="5"/>
       <c r="P91" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B92" s="3"/>
       <c r="C92" s="4"/>
-      <c r="D92" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D92" s="4"/>
       <c r="E92" s="4"/>
-      <c r="F92" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F92" s="4"/>
       <c r="N92" s="5"/>
       <c r="P92" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B93" s="3"/>
       <c r="C93" s="4"/>
-      <c r="D93" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D93" s="4"/>
       <c r="E93" s="4"/>
-      <c r="F93" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F93" s="4"/>
       <c r="N93" s="5"/>
       <c r="P93" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B94" s="3"/>
       <c r="C94" s="4"/>
-      <c r="D94" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D94" s="4"/>
       <c r="E94" s="4"/>
-      <c r="F94" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F94" s="4"/>
       <c r="N94" s="5"/>
       <c r="P94" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B95" s="3"/>
       <c r="C95" s="4"/>
-      <c r="D95" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D95" s="4"/>
       <c r="E95" s="4"/>
-      <c r="F95" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F95" s="4"/>
       <c r="N95" s="5"/>
       <c r="P95" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B96" s="3"/>
       <c r="C96" s="4"/>
-      <c r="D96" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D96" s="4"/>
       <c r="E96" s="4"/>
-      <c r="F96" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F96" s="4"/>
       <c r="N96" s="5"/>
       <c r="P96" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B97" s="3"/>
       <c r="C97" s="4"/>
-      <c r="D97" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D97" s="4"/>
       <c r="E97" s="4"/>
-      <c r="F97" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F97" s="4"/>
       <c r="N97" s="5"/>
       <c r="P97" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B98" s="3"/>
       <c r="C98" s="4"/>
-      <c r="D98" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D98" s="4"/>
       <c r="E98" s="4"/>
-      <c r="F98" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F98" s="4"/>
       <c r="N98" s="5"/>
       <c r="P98" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B99" s="3"/>
       <c r="C99" s="4"/>
-      <c r="D99" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D99" s="4"/>
       <c r="E99" s="4"/>
-      <c r="F99" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F99" s="4"/>
       <c r="N99" s="5"/>
       <c r="P99" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B100" s="3"/>
       <c r="C100" s="4"/>
-      <c r="D100" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D100" s="4"/>
       <c r="E100" s="4"/>
-      <c r="F100" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F100" s="4"/>
       <c r="N100" s="5"/>
       <c r="P100" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B101" s="3"/>
       <c r="C101" s="4"/>
-      <c r="D101" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D101" s="4"/>
       <c r="E101" s="4"/>
-      <c r="F101" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="F101" s="4"/>
       <c r="N101" s="5"/>
       <c r="P101" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B102" s="3"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="N102" s="5"/>
+      <c r="P102" s="3">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:Q102">
+    <sortCondition ref="K3:K102"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{0B525D57-0ECA-4786-93A2-CDA114163FD5}"/>
     <hyperlink ref="J3" r:id="rId2" xr:uid="{C242BF5E-28AA-4984-A4B7-40B762C44FD6}"/>
-    <hyperlink ref="I10" r:id="rId3" xr:uid="{37AC794A-8DAF-4080-859D-D090B7DD248D}"/>
-    <hyperlink ref="J10" r:id="rId4" xr:uid="{46240C68-E9E9-4D3C-9F50-86EC30CB4F7E}"/>
-    <hyperlink ref="I9" r:id="rId5" xr:uid="{5EC71679-2790-45D3-8942-A0FCA727B5EE}"/>
-    <hyperlink ref="J9" r:id="rId6" xr:uid="{09CB8FFC-A46A-411B-BB2F-563CE90AF9E9}"/>
-    <hyperlink ref="J11" r:id="rId7" xr:uid="{C5B567A9-1D79-4321-A41E-784FBB48A9FD}"/>
-    <hyperlink ref="I11" r:id="rId8" xr:uid="{D7205250-639D-45C7-A6A0-FDD3105ADBC9}"/>
-    <hyperlink ref="I12" r:id="rId9" xr:uid="{4D47AE81-F1F8-4C24-B5E3-40B5CF7B66E2}"/>
-    <hyperlink ref="J12" r:id="rId10" xr:uid="{CD53271B-12F2-4AEE-8222-E7712BFDC8BD}"/>
-    <hyperlink ref="J21" r:id="rId11" xr:uid="{B8BD528C-5F45-46F8-B2EA-10BDF231B84D}"/>
-    <hyperlink ref="I21" r:id="rId12" xr:uid="{595CE7FD-A60C-45B8-A9B4-9F4CA2A1C9F4}"/>
-    <hyperlink ref="I23" r:id="rId13" xr:uid="{DD6DDD78-65BC-4B4D-AA7F-B6AD8C8E1003}"/>
-    <hyperlink ref="J23" r:id="rId14" xr:uid="{E15F9B70-326B-4650-8AF3-93352D9C6E0D}"/>
-    <hyperlink ref="I24" r:id="rId15" xr:uid="{C3982107-C875-4457-8483-5A3ACF6A9280}"/>
-    <hyperlink ref="J24" r:id="rId16" xr:uid="{EE4D80CD-56CC-4EA4-974B-F0AAC00646A5}"/>
-    <hyperlink ref="I25" r:id="rId17" xr:uid="{E56557BE-B373-4524-8487-1E00A6257DD9}"/>
-    <hyperlink ref="J25" r:id="rId18" xr:uid="{F315D124-D5E1-4E62-9AB3-15D490E0EE99}"/>
-    <hyperlink ref="J26" r:id="rId19" xr:uid="{5F034555-1A12-48BE-AEE0-9F8FD65CEE62}"/>
-    <hyperlink ref="I26" r:id="rId20" xr:uid="{880D209A-B409-4499-BFFF-3D10FBD485E6}"/>
+    <hyperlink ref="I4" r:id="rId3" xr:uid="{37AC794A-8DAF-4080-859D-D090B7DD248D}"/>
+    <hyperlink ref="J4" r:id="rId4" xr:uid="{46240C68-E9E9-4D3C-9F50-86EC30CB4F7E}"/>
+    <hyperlink ref="I5" r:id="rId5" xr:uid="{4D47AE81-F1F8-4C24-B5E3-40B5CF7B66E2}"/>
+    <hyperlink ref="J5" r:id="rId6" xr:uid="{CD53271B-12F2-4AEE-8222-E7712BFDC8BD}"/>
+    <hyperlink ref="J6" r:id="rId7" xr:uid="{B8BD528C-5F45-46F8-B2EA-10BDF231B84D}"/>
+    <hyperlink ref="I6" r:id="rId8" xr:uid="{595CE7FD-A60C-45B8-A9B4-9F4CA2A1C9F4}"/>
+    <hyperlink ref="I7" r:id="rId9" xr:uid="{DD6DDD78-65BC-4B4D-AA7F-B6AD8C8E1003}"/>
+    <hyperlink ref="J7" r:id="rId10" xr:uid="{E15F9B70-326B-4650-8AF3-93352D9C6E0D}"/>
+    <hyperlink ref="I8" r:id="rId11" xr:uid="{C3982107-C875-4457-8483-5A3ACF6A9280}"/>
+    <hyperlink ref="J8" r:id="rId12" xr:uid="{EE4D80CD-56CC-4EA4-974B-F0AAC00646A5}"/>
+    <hyperlink ref="I9" r:id="rId13" xr:uid="{E56557BE-B373-4524-8487-1E00A6257DD9}"/>
+    <hyperlink ref="J9" r:id="rId14" xr:uid="{F315D124-D5E1-4E62-9AB3-15D490E0EE99}"/>
+    <hyperlink ref="J13" r:id="rId15" xr:uid="{5F034555-1A12-48BE-AEE0-9F8FD65CEE62}"/>
+    <hyperlink ref="I13" r:id="rId16" xr:uid="{880D209A-B409-4499-BFFF-3D10FBD485E6}"/>
+    <hyperlink ref="I10" r:id="rId17" xr:uid="{A0F16394-6F5B-494F-AE3D-9225C332E46A}"/>
+    <hyperlink ref="J10" r:id="rId18" xr:uid="{39DEC8F3-559E-47B0-A884-B8E61EEE005E}"/>
+    <hyperlink ref="I11" r:id="rId19" xr:uid="{BF21A01F-420A-4E21-AED2-167A7AA280CA}"/>
+    <hyperlink ref="J11" r:id="rId20" xr:uid="{3A4485EA-A7CA-4CD0-81B6-B30FC34487B7}"/>
+    <hyperlink ref="I12" r:id="rId21" xr:uid="{D8431750-2363-427A-A418-3CE56C76067D}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" scale="54" orientation="landscape" r:id="rId22"/>
 </worksheet>
 </file>